--- a/AAII_Financials/Quarterly/FBAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBAK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="92">
   <si>
     <t>FBAK</t>
   </si>
@@ -656,259 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>56300</v>
+        <v>56200</v>
       </c>
       <c r="E8" s="3">
         <v>56300</v>
       </c>
       <c r="F8" s="3">
+        <v>56300</v>
+      </c>
+      <c r="G8" s="3">
         <v>55700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>51900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>52200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>51000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>47300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33800</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
         <v>42700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>44500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>36600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>37900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>35600</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
-      </c>
       <c r="AE8" s="3">
         <v>0</v>
       </c>
@@ -927,8 +931,8 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
-      <c r="AK8" s="3" t="s">
-        <v>4</v>
+      <c r="AK8" s="3">
+        <v>0</v>
       </c>
       <c r="AL8" s="3" t="s">
         <v>4</v>
@@ -945,8 +949,11 @@
       <c r="AP8" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ8" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1067,53 +1074,56 @@
       <c r="AP9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>56300</v>
+        <v>56200</v>
       </c>
       <c r="E10" s="3">
         <v>56300</v>
       </c>
       <c r="F10" s="3">
+        <v>56300</v>
+      </c>
+      <c r="G10" s="3">
         <v>55700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>51900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>47300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>43900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3">
         <v>42700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>44500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1189,8 +1199,11 @@
       <c r="AP10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1233,8 +1246,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1355,8 +1369,11 @@
       <c r="AP12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1477,52 +1494,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1599,8 +1619,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1620,7 +1643,7 @@
         <v>1100</v>
       </c>
       <c r="I15" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
         <v>1300</v>
@@ -1632,10 +1655,10 @@
         <v>1300</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="N15" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>1300</v>
@@ -1644,7 +1667,7 @@
         <v>1300</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1721,8 +1744,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1762,86 +1788,87 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E17" s="3">
         <v>28000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3">
         <v>24400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1700</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
       <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3">
-        <v>0</v>
-      </c>
       <c r="AC17" s="3">
         <v>0</v>
       </c>
@@ -1866,8 +1893,8 @@
       <c r="AJ17" s="3">
         <v>0</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>4</v>
+      <c r="AK17" s="3">
+        <v>0</v>
       </c>
       <c r="AL17" s="3" t="s">
         <v>4</v>
@@ -1884,92 +1911,95 @@
       <c r="AP17" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ17" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>28300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>21700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>20200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>18300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>38500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>35000</v>
       </c>
       <c r="T18" s="3">
         <v>35000</v>
       </c>
       <c r="U18" s="3">
+        <v>35000</v>
+      </c>
+      <c r="V18" s="3">
         <v>39500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>34300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>34500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>35000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>35700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>36400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>36000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>34500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>35600</v>
       </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
       <c r="AE18" s="3">
         <v>0</v>
       </c>
@@ -1988,8 +2018,8 @@
       <c r="AJ18" s="3">
         <v>0</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>4</v>
+      <c r="AK18" s="3">
+        <v>0</v>
       </c>
       <c r="AL18" s="3" t="s">
         <v>4</v>
@@ -2006,8 +2036,11 @@
       <c r="AP18" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ18" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2050,8 +2083,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2079,63 +2113,63 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-19000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-17000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-16600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-17700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-16200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-17700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-17000</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -2154,8 +2188,8 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>4</v>
+      <c r="AK20" s="3">
+        <v>0</v>
       </c>
       <c r="AL20" s="3" t="s">
         <v>4</v>
@@ -2172,53 +2206,56 @@
       <c r="AP20" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ20" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E21" s="3">
         <v>29400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>27700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21000</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>19600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2294,8 +2331,11 @@
       <c r="AP21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2338,8 +2378,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2416,92 +2456,95 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E23" s="3">
         <v>28300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>26400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3">
         <v>18300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>18600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>19500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18600</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
         <v>0</v>
       </c>
@@ -2520,8 +2563,8 @@
       <c r="AJ23" s="3">
         <v>0</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>4</v>
+      <c r="AK23" s="3">
+        <v>0</v>
       </c>
       <c r="AL23" s="3" t="s">
         <v>4</v>
@@ -2538,8 +2581,11 @@
       <c r="AP23" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ23" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2547,121 +2593,124 @@
         <v>7100</v>
       </c>
       <c r="E24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F24" s="3">
         <v>6400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3">
         <v>4800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>4700</v>
       </c>
       <c r="Y24" s="3">
         <v>4700</v>
       </c>
       <c r="Z24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>6100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>5500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>4700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>4300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2782,92 +2831,95 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E26" s="3">
         <v>21200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3">
         <v>13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>14400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>13800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>14400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>13700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>13300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14200</v>
       </c>
-      <c r="AD26" s="3">
-        <v>0</v>
-      </c>
       <c r="AE26" s="3">
         <v>0</v>
       </c>
@@ -2886,8 +2938,8 @@
       <c r="AJ26" s="3">
         <v>0</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>4</v>
+      <c r="AK26" s="3">
+        <v>0</v>
       </c>
       <c r="AL26" s="3" t="s">
         <v>4</v>
@@ -2904,92 +2956,95 @@
       <c r="AP26" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ26" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E27" s="3">
         <v>21200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3">
         <v>13500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>13800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>13700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>13300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14200</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
         <v>0</v>
       </c>
@@ -3008,8 +3063,8 @@
       <c r="AJ27" s="3">
         <v>0</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>4</v>
+      <c r="AK27" s="3">
+        <v>0</v>
       </c>
       <c r="AL27" s="3" t="s">
         <v>4</v>
@@ -3026,8 +3081,11 @@
       <c r="AP27" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ27" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3148,8 +3206,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3234,17 +3295,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>4</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>4</v>
+      <c r="AG29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>4</v>
@@ -3252,12 +3313,12 @@
       <c r="AJ29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-4700</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>4</v>
       </c>
@@ -3270,8 +3331,11 @@
       <c r="AP29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3392,8 +3456,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3514,8 +3581,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3543,63 +3613,63 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>19000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>17000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>16600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>17700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>16200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>16400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>17700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>16500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>17000</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3618,8 +3688,8 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>4</v>
+      <c r="AK32" s="3">
+        <v>0</v>
       </c>
       <c r="AL32" s="3" t="s">
         <v>4</v>
@@ -3636,92 +3706,95 @@
       <c r="AP32" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ32" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E33" s="3">
         <v>21200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3">
         <v>13500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>13800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>13700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>13300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>15600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14200</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
         <v>0</v>
       </c>
@@ -3740,8 +3813,8 @@
       <c r="AJ33" s="3">
         <v>0</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>4</v>
+      <c r="AK33" s="3">
+        <v>0</v>
       </c>
       <c r="AL33" s="3" t="s">
         <v>4</v>
@@ -3758,8 +3831,11 @@
       <c r="AP33" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ33" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3880,92 +3956,95 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E35" s="3">
         <v>21200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3">
         <v>13500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>13800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>13700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>13300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>15600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14200</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
         <v>0</v>
       </c>
@@ -3984,8 +4063,8 @@
       <c r="AJ35" s="3">
         <v>0</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>4</v>
+      <c r="AK35" s="3">
+        <v>0</v>
       </c>
       <c r="AL35" s="3" t="s">
         <v>4</v>
@@ -4002,135 +4081,141 @@
       <c r="AP35" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ35" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4173,8 +4258,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4217,68 +4303,69 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E41" s="3">
         <v>26700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>278700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>472400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>93500</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>93500</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>93500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3">
         <v>532000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
@@ -4297,50 +4384,53 @@
       <c r="AB41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="3">
         <v>127700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH41" s="3">
         <v>108600</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL41" s="3">
         <v>134100</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AO41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP41" s="3">
         <v>79100</v>
       </c>
-      <c r="AP41" s="3" t="s">
+      <c r="AQ41" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4461,8 +4551,11 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4490,23 +4583,23 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>45000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>45000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4583,8 +4676,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4592,11 +4688,11 @@
         <v>1900</v>
       </c>
       <c r="E44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F44" s="3">
         <v>300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4627,8 +4723,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4705,35 +4801,38 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="3">
         <v>20800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4749,8 +4848,8 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4827,52 +4926,55 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>374500</v>
+      </c>
+      <c r="E46" s="3">
         <v>329100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>297800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>558700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>375300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>488000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>400600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>367600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>200900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>140300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>140300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
@@ -4949,53 +5051,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1832800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1867000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2026000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2007900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1865500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1958500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2624100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2254000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2504000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2837100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>2606000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2837100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2863900</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5071,68 +5176,71 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E48" s="3">
         <v>51200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>51700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>49000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>52600</v>
       </c>
       <c r="K48" s="3">
         <v>52600</v>
       </c>
       <c r="L48" s="3">
+        <v>52600</v>
+      </c>
+      <c r="M48" s="3">
         <v>52300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>52300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>52300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V48" s="3">
         <v>47100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
@@ -5151,97 +5259,100 @@
       <c r="AB48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD48" s="3">
         <v>50400</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH48" s="3">
         <v>46700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL48" s="3">
         <v>49500</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP48" s="3">
         <v>49200</v>
       </c>
-      <c r="AP48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>2800</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -5315,8 +5426,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5437,8 +5551,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5559,56 +5676,59 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E52" s="3">
         <v>35100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>42500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>33200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>32900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>103000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>36200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>602700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>488400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>60800</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5624,8 +5744,8 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -5681,8 +5801,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5803,130 +5926,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5123800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5084000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5099900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5244000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4923800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4997800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5557300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5116100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5213000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5337700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>5473200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5337700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5503000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5337700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5503000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5373100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5393200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5581300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5521100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5338100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4927800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4695300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4718600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4594200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3859300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3808300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3845100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3762700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3706800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3753500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3757400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3648000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3618800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3653100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3732900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3551900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3609800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>3665800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5969,8 +6098,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6013,53 +6143,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3685200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3710400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3734700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3808000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3586200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3679200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3728200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3698600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3665100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4224900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>3989800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4224900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4383800</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6135,53 +6266,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>784900</v>
+      </c>
+      <c r="E58" s="3">
         <v>738900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>739500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>804600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>731800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>743600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>896900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>865000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1001500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>671500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N58" s="3">
-        <v>671500</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>671500</v>
       </c>
       <c r="P58" s="3">
+        <v>671500</v>
+      </c>
+      <c r="Q58" s="3">
         <v>696800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6257,8 +6391,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6304,8 +6441,8 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -6379,53 +6516,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4486100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4468800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4474200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4627500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4330700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4422700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4648500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4582900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4692400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4896300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>4661400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4896300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5080600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6501,50 +6641,53 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>34000</v>
+        <v>15100</v>
       </c>
       <c r="E61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F61" s="3">
         <v>17300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>376200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>41000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>3200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -6623,53 +6766,56 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F62" s="3">
+        <v>39200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>41100</v>
+      </c>
+      <c r="J62" s="3">
         <v>4800</v>
       </c>
-      <c r="E62" s="3">
-        <v>39200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>41100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>4800</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>383300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33300</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6745,8 +6891,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6867,8 +7016,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6989,8 +7141,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7111,130 +7266,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4538600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4507500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4530700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4676300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4373700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4481200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5029400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4630900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4742300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4930200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>5044700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4930200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5113900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4930200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V66" s="3">
         <v>5026800</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z66" s="3">
         <v>4108700</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD66" s="3">
         <v>3260600</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH66" s="3">
         <v>3246600</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL66" s="3">
         <v>3156300</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AO66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP66" s="3">
         <v>3117100</v>
       </c>
-      <c r="AP66" s="3" t="s">
+      <c r="AQ66" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7277,8 +7438,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7399,8 +7561,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7521,8 +7686,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7643,8 +7811,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7765,92 +7936,95 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>538700</v>
+      </c>
+      <c r="E72" s="3">
         <v>530600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>522100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>527400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>518700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>507900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>508200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>500400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>494800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>482200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>482200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>482200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V72" s="3">
         <v>474600</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z72" s="3">
         <v>466900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD72" s="3">
         <v>460100</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7869,26 +8043,29 @@
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3">
         <v>433300</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP72" s="3">
         <v>427300</v>
       </c>
-      <c r="AP72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8009,8 +8186,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8131,8 +8311,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8253,130 +8436,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>585200</v>
+      </c>
+      <c r="E76" s="3">
         <v>576400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>569200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>567700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>550100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>516600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>527900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>485200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>470700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>407600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>428600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>407600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>389100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>407600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>389100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>444200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>474000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>554500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>565100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>577300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>571100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>586600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>585400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>590000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>575800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>547700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>545700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>534700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>518700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>506900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>493000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>489700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>488700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>496900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>511700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>506200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>499000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>492700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>519100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8497,219 +8686,225 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E81" s="3">
         <v>21200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3">
         <v>13500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>13800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>13700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>13300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>15600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14200</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
         <v>0</v>
       </c>
@@ -8728,8 +8923,8 @@
       <c r="AJ81" s="3">
         <v>0</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>4</v>
+      <c r="AK81" s="3">
+        <v>0</v>
       </c>
       <c r="AL81" s="3" t="s">
         <v>4</v>
@@ -8746,8 +8941,11 @@
       <c r="AP81" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ81" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8790,8 +8988,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8834,8 +9033,8 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8912,8 +9111,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9034,8 +9236,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9156,8 +9361,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9278,8 +9486,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9400,8 +9611,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9522,8 +9736,11 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9566,8 +9783,8 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -9644,8 +9861,11 @@
       <c r="AP89" s="3">
         <v>0</v>
       </c>
+      <c r="AQ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9688,8 +9908,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9732,8 +9953,8 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9810,8 +10031,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9932,8 +10156,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10054,8 +10281,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10098,8 +10328,8 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -10176,8 +10406,11 @@
       <c r="AP94" s="3">
         <v>0</v>
       </c>
+      <c r="AQ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10220,8 +10453,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10264,8 +10498,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10342,8 +10576,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10464,8 +10701,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10586,8 +10826,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10708,8 +10951,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10752,8 +10998,8 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -10830,8 +11076,11 @@
       <c r="AP100" s="3">
         <v>0</v>
       </c>
+      <c r="AQ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10874,8 +11123,8 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10952,8 +11201,11 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10996,8 +11248,8 @@
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -11072,6 +11324,9 @@
         <v>0</v>
       </c>
       <c r="AP102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="3">
         <v>0</v>
       </c>
     </row>
